--- a/Output/Baseline/Data_files/bia_baseline.xlsx
+++ b/Output/Baseline/Data_files/bia_baseline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gustavosplmoura/Library/Mobile Documents/com~apple~CloudDocs/Medicina/Biblioteca/Research/Data Science/Data Science/PROJECTS/DVEP/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gustavosplmoura/Library/Mobile Documents/com~apple~CloudDocs/Medicina/Biblioteca/Research/Data Science/Data Science/PROJECTS/DVEP/Output/Baseline/Data_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC861623-B37F-7148-B48D-306AAFE0A29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E9FAAB-BE70-6841-A9DC-0103A567DE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="6080" windowWidth="28580" windowHeight="19060" activeTab="2" xr2:uid="{FD799774-BD8C-8548-A615-459C767A3F24}"/>
+    <workbookView xWindow="12540" yWindow="1440" windowWidth="28580" windowHeight="23700" activeTab="3" xr2:uid="{FD799774-BD8C-8548-A615-459C767A3F24}"/>
   </bookViews>
   <sheets>
     <sheet name="bia_baseline" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="368">
   <si>
     <t>record_id</t>
   </si>
@@ -853,24 +853,6 @@
     <t>Valor p2</t>
   </si>
   <si>
-    <t>6.5 (6.1–6.8)</t>
-  </si>
-  <si>
-    <t>538.2 (519.3–557)</t>
-  </si>
-  <si>
-    <t>60.8 (57.8–63.8)</t>
-  </si>
-  <si>
-    <t>92 (87.5–96.4)</t>
-  </si>
-  <si>
-    <t>1.3 (1.3–1.4)</t>
-  </si>
-  <si>
-    <t>35.2 (31–39.4)</t>
-  </si>
-  <si>
     <t>9.1 (8.7–9.4)</t>
   </si>
   <si>
@@ -880,115 +862,10 @@
     <t>1879.9 (1720.9–2039)</t>
   </si>
   <si>
-    <t>41.6 (37.6–45.6)</t>
-  </si>
-  <si>
-    <t>16.5 (12.7–20.2)</t>
-  </si>
-  <si>
-    <t>44.7 (42.6–46.8)</t>
-  </si>
-  <si>
-    <t>50.4 (48.1–52.7)</t>
-  </si>
-  <si>
-    <t>18.7 (18–19.5)</t>
-  </si>
-  <si>
-    <t>55.3 (53.2–57.4)</t>
-  </si>
-  <si>
-    <t>24.4 (23–25.8)</t>
-  </si>
-  <si>
-    <t>11.1 (10.3–11.8)</t>
-  </si>
-  <si>
-    <t>1.3 (1.2–1.5)</t>
-  </si>
-  <si>
-    <t>5.2 (4.9–5.4)</t>
-  </si>
-  <si>
-    <t>5.4 (5.1–5.7)</t>
-  </si>
-  <si>
-    <t>2.2 (1.9–2.5)</t>
-  </si>
-  <si>
-    <t>37.8 (36.2–39.4)</t>
-  </si>
-  <si>
-    <t>16.6 (16.1–17.2)</t>
-  </si>
-  <si>
-    <t>6.3 (5.9–6.6)</t>
-  </si>
-  <si>
-    <t>556.6 (537.3–575.9)</t>
-  </si>
-  <si>
-    <t>60.8 (57.5–64.1)</t>
-  </si>
-  <si>
-    <t>88.7 (85.7–91.7)</t>
-  </si>
-  <si>
-    <t>1 (0.9–1)</t>
-  </si>
-  <si>
-    <t>33.1 (32.4–33.9)</t>
-  </si>
-  <si>
     <t>9.2 (8.8–9.6)</t>
   </si>
   <si>
     <t>1915.8 (1803.4–2028.3)</t>
-  </si>
-  <si>
-    <t>43.1 (40–46.1)</t>
-  </si>
-  <si>
-    <t>16.1 (14.9–17.3)</t>
-  </si>
-  <si>
-    <t>48.6 (45.2–52.1)</t>
-  </si>
-  <si>
-    <t>45.6 (42.4–48.9)</t>
-  </si>
-  <si>
-    <t>17 (15.9–18.2)</t>
-  </si>
-  <si>
-    <t>51.4 (47.9–54.8)</t>
-  </si>
-  <si>
-    <t>21.9 (19.9–24)</t>
-  </si>
-  <si>
-    <t>9.7 (8.6–10.8)</t>
-  </si>
-  <si>
-    <t>1.3 (1.2–1.3)</t>
-  </si>
-  <si>
-    <t>1.3 (1.1–1.4)</t>
-  </si>
-  <si>
-    <t>4.8 (4.3–5.2)</t>
-  </si>
-  <si>
-    <t>4.9 (4.4–5.4)</t>
-  </si>
-  <si>
-    <t>2.3 (2–2.5)</t>
-  </si>
-  <si>
-    <t>34.2 (31.6–36.8)</t>
-  </si>
-  <si>
-    <t>15.3 (14.2–16.3)</t>
   </si>
   <si>
     <t>Grupo placebo
@@ -1069,6 +946,204 @@
   </si>
   <si>
     <t>Água Extracelular (L)</t>
+  </si>
+  <si>
+    <t>1,6 (1,6–1,7)</t>
+  </si>
+  <si>
+    <t>0,727</t>
+  </si>
+  <si>
+    <t>92 (87,5–96,4)</t>
+  </si>
+  <si>
+    <t>88,7 (85,7–91,7)</t>
+  </si>
+  <si>
+    <t>0,243</t>
+  </si>
+  <si>
+    <t>35,2 (31–39,4)</t>
+  </si>
+  <si>
+    <t>33,1 (32,4–33,9)</t>
+  </si>
+  <si>
+    <t>0,349</t>
+  </si>
+  <si>
+    <t>1 (0,9–1)</t>
+  </si>
+  <si>
+    <t>0,139</t>
+  </si>
+  <si>
+    <t>1,3 (1,3–1,4)</t>
+  </si>
+  <si>
+    <t>1,4 (1,3–1,4)</t>
+  </si>
+  <si>
+    <t>0,645</t>
+  </si>
+  <si>
+    <t>6,5 (6,1–6,8)</t>
+  </si>
+  <si>
+    <t>6,3 (5,9–6,6)</t>
+  </si>
+  <si>
+    <t>0,354</t>
+  </si>
+  <si>
+    <t>538,2 (519,3–557)</t>
+  </si>
+  <si>
+    <t>556,6 (537,3–575,9)</t>
+  </si>
+  <si>
+    <t>0,185</t>
+  </si>
+  <si>
+    <t>60,8 (57,8–63,8)</t>
+  </si>
+  <si>
+    <t>60,8 (57,5–64,1)</t>
+  </si>
+  <si>
+    <t>0,988</t>
+  </si>
+  <si>
+    <t>41,6 (37,6–45,6)</t>
+  </si>
+  <si>
+    <t>43,1 (40–46,1)</t>
+  </si>
+  <si>
+    <t>0,571</t>
+  </si>
+  <si>
+    <t>16,5 (12,7–20,2)</t>
+  </si>
+  <si>
+    <t>16,1 (14,9–17,3)</t>
+  </si>
+  <si>
+    <t>0,869</t>
+  </si>
+  <si>
+    <t>44,7 (42,6–46,8)</t>
+  </si>
+  <si>
+    <t>48,6 (45,2–52,1)</t>
+  </si>
+  <si>
+    <t>0,062</t>
+  </si>
+  <si>
+    <t>2,2 (1,9–2,5)</t>
+  </si>
+  <si>
+    <t>2,3 (2–2,5)</t>
+  </si>
+  <si>
+    <t>0,785</t>
+  </si>
+  <si>
+    <t>50,4 (48,1–52,7)</t>
+  </si>
+  <si>
+    <t>45,6 (42,4–48,9)</t>
+  </si>
+  <si>
+    <t>0,025*</t>
+  </si>
+  <si>
+    <t>18,7 (18–19,5)</t>
+  </si>
+  <si>
+    <t>17 (15,9–18,2)</t>
+  </si>
+  <si>
+    <t>0,016*</t>
+  </si>
+  <si>
+    <t>55,3 (53,2–57,4)</t>
+  </si>
+  <si>
+    <t>51,4 (47,9–54,8)</t>
+  </si>
+  <si>
+    <t>24,4 (23–25,8)</t>
+  </si>
+  <si>
+    <t>21,9 (19,9–24)</t>
+  </si>
+  <si>
+    <t>0,054</t>
+  </si>
+  <si>
+    <t>11,1 (10,3–11,8)</t>
+  </si>
+  <si>
+    <t>9,7 (8,6–10,8)</t>
+  </si>
+  <si>
+    <t>0,044*</t>
+  </si>
+  <si>
+    <t>1,4 (1,2–1,5)</t>
+  </si>
+  <si>
+    <t>1,3 (1,2–1,3)</t>
+  </si>
+  <si>
+    <t>0,165</t>
+  </si>
+  <si>
+    <t>1,3 (1,2–1,5)</t>
+  </si>
+  <si>
+    <t>1,3 (1,1–1,4)</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>5,2 (4,9–5,4)</t>
+  </si>
+  <si>
+    <t>4,8 (4,3–5,2)</t>
+  </si>
+  <si>
+    <t>0,117</t>
+  </si>
+  <si>
+    <t>5,4 (5,1–5,7)</t>
+  </si>
+  <si>
+    <t>4,9 (4,4–5,4)</t>
+  </si>
+  <si>
+    <t>0,102</t>
+  </si>
+  <si>
+    <t>37,8 (36,2–39,4)</t>
+  </si>
+  <si>
+    <t>34,2 (31,6–36,8)</t>
+  </si>
+  <si>
+    <t>0,024*</t>
+  </si>
+  <si>
+    <t>16,6 (16,1–17,2)</t>
+  </si>
+  <si>
+    <t>15,3 (14,2–16,3)</t>
+  </si>
+  <si>
+    <t>0,031*</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1299,7 @@
       <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1416,8 +1491,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1620,6 +1701,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1665,7 +1826,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1678,22 +1839,14 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1704,15 +1857,25 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="33" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1758,7 +1921,12 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8857,8 +9025,8 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="22" t="s">
-        <v>320</v>
+      <c r="B3" s="14" t="s">
+        <v>279</v>
       </c>
       <c r="C3" t="s">
         <v>140</v>
@@ -8879,11 +9047,11 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="K3" s="23"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B4" s="23" t="s">
-        <v>321</v>
+      <c r="B4" s="15" t="s">
+        <v>280</v>
       </c>
       <c r="C4" t="s">
         <v>138</v>
@@ -8904,11 +9072,11 @@
       <c r="H4">
         <v>1.8E-3</v>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B5" s="23" t="s">
-        <v>322</v>
+      <c r="B5" s="15" t="s">
+        <v>281</v>
       </c>
       <c r="C5" t="s">
         <v>146</v>
@@ -8929,11 +9097,11 @@
       <c r="H5">
         <v>0.17760000000000001</v>
       </c>
-      <c r="K5" s="23"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B6" s="23" t="s">
-        <v>323</v>
+      <c r="B6" s="15" t="s">
+        <v>282</v>
       </c>
       <c r="C6" t="s">
         <v>211</v>
@@ -8954,11 +9122,11 @@
       <c r="H6">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="K6" s="23"/>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="23" t="s">
-        <v>324</v>
+      <c r="B7" s="15" t="s">
+        <v>283</v>
       </c>
       <c r="C7" t="s">
         <v>144</v>
@@ -8979,11 +9147,11 @@
       <c r="H7">
         <v>0.64359999999999995</v>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="15"/>
     </row>
     <row r="8" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="23" t="s">
-        <v>325</v>
+      <c r="B8" s="15" t="s">
+        <v>284</v>
       </c>
       <c r="C8" t="s">
         <v>132</v>
@@ -9004,11 +9172,11 @@
       <c r="H8">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="K8" s="22"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B9" s="23" t="s">
-        <v>326</v>
+      <c r="B9" s="15" t="s">
+        <v>285</v>
       </c>
       <c r="C9" t="s">
         <v>134</v>
@@ -9029,11 +9197,11 @@
       <c r="H9">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B10" s="23" t="s">
-        <v>327</v>
+      <c r="B10" s="15" t="s">
+        <v>286</v>
       </c>
       <c r="C10" t="s">
         <v>136</v>
@@ -9054,11 +9222,11 @@
       <c r="H10">
         <v>4.0099999999999997E-2</v>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B11" s="23" t="s">
-        <v>328</v>
+      <c r="B11" s="15" t="s">
+        <v>287</v>
       </c>
       <c r="C11" t="s">
         <v>154</v>
@@ -9079,11 +9247,11 @@
       <c r="H11">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="K11" s="23"/>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B12" s="23" t="s">
-        <v>329</v>
+      <c r="B12" s="15" t="s">
+        <v>288</v>
       </c>
       <c r="C12" t="s">
         <v>156</v>
@@ -9104,11 +9272,11 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="K12" s="23"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B13" s="23" t="s">
-        <v>330</v>
+      <c r="B13" s="15" t="s">
+        <v>289</v>
       </c>
       <c r="C13" t="s">
         <v>158</v>
@@ -9129,11 +9297,11 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B14" s="23" t="s">
-        <v>331</v>
+      <c r="B14" s="15" t="s">
+        <v>290</v>
       </c>
       <c r="C14" t="s">
         <v>171</v>
@@ -9156,8 +9324,8 @@
       </c>
     </row>
     <row r="15" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B15" s="23" t="s">
-        <v>332</v>
+      <c r="B15" s="15" t="s">
+        <v>291</v>
       </c>
       <c r="C15" t="s">
         <v>160</v>
@@ -9178,11 +9346,11 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="K15" s="23"/>
+      <c r="K15" s="15"/>
     </row>
     <row r="16" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B16" s="23" t="s">
-        <v>333</v>
+      <c r="B16" s="15" t="s">
+        <v>292</v>
       </c>
       <c r="C16" t="s">
         <v>162</v>
@@ -9203,11 +9371,11 @@
       <c r="H16">
         <v>1E-4</v>
       </c>
-      <c r="K16" s="23"/>
+      <c r="K16" s="15"/>
     </row>
     <row r="17" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B17" s="23" t="s">
-        <v>334</v>
+      <c r="B17" s="15" t="s">
+        <v>293</v>
       </c>
       <c r="C17" t="s">
         <v>164</v>
@@ -9228,11 +9396,11 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="K17" s="23"/>
+      <c r="K17" s="15"/>
     </row>
     <row r="18" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B18" s="23" t="s">
-        <v>335</v>
+      <c r="B18" s="15" t="s">
+        <v>294</v>
       </c>
       <c r="C18" t="s">
         <v>217</v>
@@ -9253,11 +9421,11 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="K18" s="23"/>
+      <c r="K18" s="15"/>
     </row>
     <row r="19" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B19" s="23" t="s">
-        <v>336</v>
+      <c r="B19" s="15" t="s">
+        <v>295</v>
       </c>
       <c r="C19" t="s">
         <v>212</v>
@@ -9278,11 +9446,11 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="K19" s="23"/>
+      <c r="K19" s="15"/>
     </row>
     <row r="20" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B20" s="23" t="s">
-        <v>337</v>
+      <c r="B20" s="15" t="s">
+        <v>296</v>
       </c>
       <c r="C20" t="s">
         <v>213</v>
@@ -9303,11 +9471,11 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="K20" s="23"/>
+      <c r="K20" s="15"/>
     </row>
     <row r="21" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B21" s="23" t="s">
-        <v>338</v>
+      <c r="B21" s="15" t="s">
+        <v>297</v>
       </c>
       <c r="C21" t="s">
         <v>214</v>
@@ -9328,11 +9496,11 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="K21" s="23"/>
+      <c r="K21" s="15"/>
     </row>
     <row r="22" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B22" s="23" t="s">
-        <v>339</v>
+      <c r="B22" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="C22" t="s">
         <v>215</v>
@@ -9353,11 +9521,11 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="K22" s="23"/>
+      <c r="K22" s="15"/>
     </row>
     <row r="23" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="23" t="s">
-        <v>340</v>
+      <c r="B23" s="15" t="s">
+        <v>299</v>
       </c>
       <c r="C23" t="s">
         <v>216</v>
@@ -9378,11 +9546,11 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="K23" s="24"/>
+      <c r="K23" s="16"/>
     </row>
     <row r="24" spans="2:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="B24" s="23" t="s">
-        <v>341</v>
+      <c r="B24" s="15" t="s">
+        <v>300</v>
       </c>
       <c r="C24" t="s">
         <v>173</v>
@@ -9405,8 +9573,8 @@
       </c>
     </row>
     <row r="25" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="24" t="s">
-        <v>342</v>
+      <c r="B25" s="16" t="s">
+        <v>301</v>
       </c>
       <c r="C25" t="s">
         <v>175</v>
@@ -9448,7 +9616,7 @@
       <c r="H31">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="K31" s="23"/>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" spans="2:11" ht="14" x14ac:dyDescent="0.15">
       <c r="C32" t="s">
@@ -9470,7 +9638,7 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="K32" s="23"/>
+      <c r="K32" s="15"/>
     </row>
     <row r="33" spans="3:11" ht="14" x14ac:dyDescent="0.15">
       <c r="C33" t="s">
@@ -9492,11 +9660,11 @@
       <c r="H33">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="K33" s="23"/>
+      <c r="K33" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G1:H1 H1:H1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9517,53 +9685,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="17" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26">
+      <c r="A2" s="10">
         <v>2</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="D2" s="28" t="s">
+      <c r="C2" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="11">
         <v>-1.21</v>
       </c>
       <c r="G2">
         <f>IF(H2&lt;0.001,"&lt; 0.001*",IF(H2&lt;0.05,CONCATENATE(ROUND(H2,3),"*"),ROUND(H2,3)))</f>
         <v>0.26700000000000002</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="19">
         <v>0.26690000000000003</v>
       </c>
       <c r="L2" s="4"/>
@@ -9573,29 +9741,29 @@
       <c r="P2" s="4"/>
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.15">
-      <c r="A3" s="30">
+      <c r="A3" s="12">
         <v>3</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="D3" s="31" t="s">
+      <c r="C3" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="13">
         <v>-2.72</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" ref="G3:G24" si="0">IF(H3&lt;0.001,"&lt; 0.001*",IF(H3&lt;0.05,CONCATENATE(ROUND(H3,3),"*"),ROUND(H3,3)))</f>
         <v>0.026*</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="20">
         <v>2.64E-2</v>
       </c>
       <c r="L3" s="4"/>
@@ -9605,29 +9773,29 @@
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26">
+      <c r="A4" s="10">
         <v>4</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="D4" s="31" t="s">
+      <c r="C4" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="13">
         <v>-2.85</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="0"/>
         <v>0.026*</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="20">
         <v>2.5700000000000001E-2</v>
       </c>
       <c r="L4" s="5"/>
@@ -9637,623 +9805,623 @@
       <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A5" s="30">
+      <c r="A5" s="12">
         <v>5</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="C5" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="13">
         <v>-0.38</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
         <v>0.72599999999999998</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="20">
         <v>0.7258</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A6" s="26">
+      <c r="A6" s="10">
         <v>6</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="11">
         <v>-0.21</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
         <v>0.84299999999999997</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="19">
         <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A7" s="30">
+      <c r="A7" s="12">
         <v>7</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="D7" s="28" t="s">
+      <c r="C7" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="11">
         <v>2.54</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
         <v>0.035*</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="19">
         <v>3.49E-2</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A8" s="26">
+      <c r="A8" s="10">
         <v>8</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="13">
         <v>1.74</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
         <v>0.122</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="20">
         <v>0.1222</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A9" s="30">
+      <c r="A9" s="12">
         <v>9</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="C9" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="11">
         <v>2.82</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="0"/>
         <v>0.026*</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="19">
         <v>2.58E-2</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A10" s="30">
+      <c r="A10" s="12">
         <v>13</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="D10" s="31" t="s">
+      <c r="C10" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="13">
         <v>-0.09</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
         <v>0.93400000000000005</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="20">
         <v>0.93440000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A11" s="26">
+      <c r="A11" s="10">
         <v>14</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="D11" s="28" t="s">
+      <c r="C11" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="11">
         <v>0.21</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
         <v>0.84599999999999997</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="19">
         <v>0.84560000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A12" s="30">
+      <c r="A12" s="12">
         <v>15</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="D12" s="31" t="s">
+      <c r="C12" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="13">
         <v>1.01</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
         <v>0.36199999999999999</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="20">
         <v>0.36199999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A13" s="26">
+      <c r="A13" s="10">
         <v>16</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="D13" s="31" t="s">
+      <c r="C13" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="13">
         <v>0.41</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
         <v>0.71</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="20">
         <v>0.71030000000000004</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A14" s="30">
+      <c r="A14" s="12">
         <v>17</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C14" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="D14" s="28" t="s">
+      <c r="C14" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="11">
         <v>-2.89</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="0"/>
         <v>0.021*</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="19">
         <v>2.0500000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A15" s="26">
+      <c r="A15" s="10">
         <v>18</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="D15" s="31" t="s">
+      <c r="C15" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="13">
         <v>-2.5499999999999998</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="0"/>
         <v>0.045*</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="20">
         <v>4.48E-2</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="14" x14ac:dyDescent="0.15">
-      <c r="A16" s="30">
+      <c r="A16" s="12">
         <v>19</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="11">
         <v>-1.01</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
         <v>0.36199999999999999</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="19">
         <v>0.36199999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A17" s="26">
+      <c r="A17" s="10">
         <v>20</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="D17" s="31" t="s">
+      <c r="C17" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="13">
         <v>-2.66</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="0"/>
         <v>0.029*</v>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="20">
         <v>2.8899999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A18" s="30">
+      <c r="A18" s="12">
         <v>21</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="D18" s="28" t="s">
+      <c r="C18" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="11">
         <v>-1.77</v>
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
         <v>0.11799999999999999</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="19">
         <v>0.1177</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A19" s="26">
+      <c r="A19" s="10">
         <v>22</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="23" t="s">
-        <v>337</v>
-      </c>
-      <c r="D19" s="31" t="s">
+      <c r="C19" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="13">
         <v>-2.0699999999999998</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="20">
         <v>7.5600000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A20" s="30">
+      <c r="A20" s="12">
         <v>23</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D20" s="28" t="s">
+      <c r="C20" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="11">
         <v>-2.6</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="0"/>
         <v>0.032*</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="19">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A21" s="26">
+      <c r="A21" s="10">
         <v>24</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="C21" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D21" s="31" t="s">
+      <c r="C21" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="13">
         <v>-2.64</v>
       </c>
       <c r="G21">
         <f t="shared" si="0"/>
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="20">
         <v>7.2900000000000006E-2</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A22" s="30">
+      <c r="A22" s="12">
         <v>25</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="D22" s="28" t="s">
+      <c r="C22" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="11">
         <v>-2.96</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="0"/>
         <v>0.036*</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="19">
         <v>3.6400000000000002E-2</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A23" s="26">
+      <c r="A23" s="10">
         <v>26</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="D23" s="28" t="s">
+      <c r="C23" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="11">
         <v>-2.79</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="0"/>
         <v>0.025*</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="19">
         <v>2.4500000000000001E-2</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20">
+      <c r="A24" s="6">
         <v>27</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="D24" s="21" t="s">
+      <c r="C24" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="7">
         <v>-3.13</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="0"/>
         <v>0.016*</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="22">
         <v>1.5699999999999999E-2</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A33" s="26">
+      <c r="A33" s="10">
         <v>10</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="11">
         <v>-0.6</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="11">
         <f>IF(H33&lt;0.05,CONCATENATE(ROUND(H33,3),"*"),ROUND(H33,3))</f>
         <v>0.58299999999999996</v>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="19">
         <v>0.58260000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A34" s="30">
+      <c r="A34" s="12">
         <v>11</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31" t="s">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="E34" s="31" t="s">
+      <c r="E34" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="13">
         <v>-2.33</v>
       </c>
-      <c r="G34" s="31" t="str">
+      <c r="G34" s="13" t="str">
         <f>IF(H34&lt;0.05,CONCATENATE(ROUND(H34,3),"*"),ROUND(H34,3))</f>
         <v>0.048*</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="20">
         <v>4.8300000000000003E-2</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A35" s="26">
+      <c r="A35" s="10">
         <v>12</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28" t="s">
+      <c r="C35" s="11"/>
+      <c r="D35" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="11">
         <v>-0.43</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="11">
         <f>IF(H35&lt;0.05,CONCATENATE(ROUND(H35,3),"*"),ROUND(H35,3))</f>
         <v>0.69</v>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="19">
         <v>0.68989999999999996</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10264,743 +10432,1535 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFB1076-8356-7A4B-BA71-77A67C3F751C}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="54.5" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1" s="32" t="str">
+        <f>TRIM(A1)</f>
+        <v>Parâmetro</v>
+      </c>
+      <c r="G1" s="32" t="str">
+        <f t="shared" ref="G1:I16" si="0">TRIM(B1)</f>
+        <v>Grupo placebo
+média (IC 95%)</v>
+      </c>
+      <c r="H1" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Grupo Eclipta
+média (IC 95%)</v>
+      </c>
+      <c r="I1" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Valor p</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F2" s="32" t="str">
+        <f t="shared" ref="F2:F24" si="1">TRIM(A2)</f>
+        <v>Altura (m)</v>
+      </c>
+      <c r="G2" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>1,6 (1,6–1,7)</v>
+      </c>
+      <c r="H2" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>1,6 (1,6–1,7)</v>
+      </c>
+      <c r="I2" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,727</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F3" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Peso (kg)</v>
+      </c>
+      <c r="G3" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>92 (87,5–96,4)</v>
+      </c>
+      <c r="H3" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>88,7 (85,7–91,7)</v>
+      </c>
+      <c r="I3" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F4" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Índice de Massa Corporal (kg/m²)</v>
+      </c>
+      <c r="G4" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>35,2 (31–39,4)</v>
+      </c>
+      <c r="H4" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>33,1 (32,4–33,9)</v>
+      </c>
+      <c r="I4" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Circunferência Abdominal (m)</v>
+      </c>
+      <c r="G5" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>1 (1–1)</v>
+      </c>
+      <c r="H5" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>1 (0,9–1)</v>
+      </c>
+      <c r="I5" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F6" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Nível de Atividade Física (PAL)</v>
+      </c>
+      <c r="G6" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>1,3 (1,3–1,4)</v>
+      </c>
+      <c r="H6" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>1,4 (1,3–1,4)</v>
+      </c>
+      <c r="I6" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,645</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D7" t="s">
+        <v>317</v>
+      </c>
+      <c r="F7" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Ângulo de Fase (°)</v>
+      </c>
+      <c r="G7" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>6,5 (6,1–6,8)</v>
+      </c>
+      <c r="H7" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>6,3 (5,9–6,6)</v>
+      </c>
+      <c r="I7" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="D8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F8" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Resistência (Ω)</v>
+      </c>
+      <c r="G8" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>538,2 (519,3–557)</v>
+      </c>
+      <c r="H8" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>556,6 (537,3–575,9)</v>
+      </c>
+      <c r="I8" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D9" t="s">
+        <v>323</v>
+      </c>
+      <c r="F9" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Reatância (Ω)</v>
+      </c>
+      <c r="G9" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>60,8 (57,8–63,8)</v>
+      </c>
+      <c r="H9" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>60,8 (57,5–64,1)</v>
+      </c>
+      <c r="I9" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,988</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" t="s">
+        <v>326</v>
+      </c>
+      <c r="F10" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Massa gorda Absoluta (kg)</v>
+      </c>
+      <c r="G10" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>41,6 (37,6–45,6)</v>
+      </c>
+      <c r="H10" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>43,1 (40–46,1)</v>
+      </c>
+      <c r="I10" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,571</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C11" t="s">
+        <v>328</v>
+      </c>
+      <c r="D11" t="s">
+        <v>329</v>
+      </c>
+      <c r="F11" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Índice de Massa gorda (kg/m²)</v>
+      </c>
+      <c r="G11" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>16,5 (12,7–20,2)</v>
+      </c>
+      <c r="H11" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>16,1 (14,9–17,3)</v>
+      </c>
+      <c r="I11" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,869</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C12" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" t="s">
+        <v>332</v>
+      </c>
+      <c r="F12" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Massa gorda Relativa (%)</v>
+      </c>
+      <c r="G12" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>44,7 (42,6–46,8)</v>
+      </c>
+      <c r="H12" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>48,6 (45,2–52,1)</v>
+      </c>
+      <c r="I12" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,062</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B13" t="s">
+        <v>333</v>
+      </c>
+      <c r="C13" t="s">
+        <v>334</v>
+      </c>
+      <c r="D13" t="s">
+        <v>335</v>
+      </c>
+      <c r="F13" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Tecido Adiposo Visceral (kg)</v>
+      </c>
+      <c r="G13" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>2,2 (1,9–2,5)</v>
+      </c>
+      <c r="H13" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>2,3 (2–2,5)</v>
+      </c>
+      <c r="I13" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,785</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14" t="s">
+        <v>337</v>
+      </c>
+      <c r="D14" t="s">
+        <v>338</v>
+      </c>
+      <c r="F14" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Massa Livre de Gordura Absoluta (kg)</v>
+      </c>
+      <c r="G14" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>50,4 (48,1–52,7)</v>
+      </c>
+      <c r="H14" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>45,6 (42,4–48,9)</v>
+      </c>
+      <c r="I14" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,025*</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" t="s">
+        <v>339</v>
+      </c>
+      <c r="C15" t="s">
+        <v>340</v>
+      </c>
+      <c r="D15" t="s">
+        <v>341</v>
+      </c>
+      <c r="F15" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Índice de Massa Livre de Gordura (kg/m²)</v>
+      </c>
+      <c r="G15" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>18,7 (18–19,5)</v>
+      </c>
+      <c r="H15" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>17 (15,9–18,2)</v>
+      </c>
+      <c r="I15" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,016*</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C16" t="s">
+        <v>343</v>
+      </c>
+      <c r="D16" t="s">
+        <v>332</v>
+      </c>
+      <c r="F16" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Massa Livre de Gordura Relativa (%)</v>
+      </c>
+      <c r="G16" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>55,3 (53,2–57,4)</v>
+      </c>
+      <c r="H16" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>51,4 (47,9–54,8)</v>
+      </c>
+      <c r="I16" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>0,062</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" t="s">
+        <v>344</v>
+      </c>
+      <c r="C17" t="s">
+        <v>345</v>
+      </c>
+      <c r="D17" t="s">
+        <v>346</v>
+      </c>
+      <c r="F17" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>MME Corporal Total (kg)</v>
+      </c>
+      <c r="G17" s="32" t="str">
+        <f t="shared" ref="G17:G24" si="2">TRIM(B17)</f>
+        <v>24,4 (23–25,8)</v>
+      </c>
+      <c r="H17" s="32" t="str">
+        <f t="shared" ref="H17:H24" si="3">TRIM(C17)</f>
+        <v>21,9 (19,9–24)</v>
+      </c>
+      <c r="I17" s="32" t="str">
+        <f t="shared" ref="I17:I24" si="4">TRIM(D17)</f>
+        <v>0,054</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B18" t="s">
+        <v>347</v>
+      </c>
+      <c r="C18" t="s">
+        <v>348</v>
+      </c>
+      <c r="D18" t="s">
+        <v>349</v>
+      </c>
+      <c r="F18" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>MME do Tronco (kg)</v>
+      </c>
+      <c r="G18" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>11,1 (10,3–11,8)</v>
+      </c>
+      <c r="H18" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>9,7 (8,6–10,8)</v>
+      </c>
+      <c r="I18" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>0,044*</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>296</v>
+      </c>
+      <c r="B19" t="s">
+        <v>350</v>
+      </c>
+      <c r="C19" t="s">
+        <v>351</v>
+      </c>
+      <c r="D19" t="s">
+        <v>352</v>
+      </c>
+      <c r="F19" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>MME do Braço Direito (kg)</v>
+      </c>
+      <c r="G19" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>1,4 (1,2–1,5)</v>
+      </c>
+      <c r="H19" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>1,3 (1,2–1,3)</v>
+      </c>
+      <c r="I19" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>0,165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" t="s">
+        <v>354</v>
+      </c>
+      <c r="D20" t="s">
+        <v>355</v>
+      </c>
+      <c r="F20" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>MME do Braço Esquerdo (kg)</v>
+      </c>
+      <c r="G20" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>1,3 (1,2–1,5)</v>
+      </c>
+      <c r="H20" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>1,3 (1,1–1,4)</v>
+      </c>
+      <c r="I20" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>0,3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" t="s">
+        <v>357</v>
+      </c>
+      <c r="D21" t="s">
+        <v>358</v>
+      </c>
+      <c r="F21" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>MME da Perna Direita (kg)</v>
+      </c>
+      <c r="G21" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>5,2 (4,9–5,4)</v>
+      </c>
+      <c r="H21" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>4,8 (4,3–5,2)</v>
+      </c>
+      <c r="I21" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>0,117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" t="s">
+        <v>359</v>
+      </c>
+      <c r="C22" t="s">
+        <v>360</v>
+      </c>
+      <c r="D22" t="s">
+        <v>361</v>
+      </c>
+      <c r="F22" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>MME da Perna Esquerda (kg)</v>
+      </c>
+      <c r="G22" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>5,4 (5,1–5,7)</v>
+      </c>
+      <c r="H22" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>4,9 (4,4–5,4)</v>
+      </c>
+      <c r="I22" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>0,102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B23" t="s">
+        <v>362</v>
+      </c>
+      <c r="C23" t="s">
+        <v>363</v>
+      </c>
+      <c r="D23" t="s">
+        <v>364</v>
+      </c>
+      <c r="F23" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Água Corporal Total (L)</v>
+      </c>
+      <c r="G23" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>37,8 (36,2–39,4)</v>
+      </c>
+      <c r="H23" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>34,2 (31,6–36,8)</v>
+      </c>
+      <c r="I23" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>0,024*</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" t="s">
+        <v>365</v>
+      </c>
+      <c r="C24" t="s">
+        <v>366</v>
+      </c>
+      <c r="D24" t="s">
+        <v>367</v>
+      </c>
+      <c r="F24" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Água Extracelular (L)</v>
+      </c>
+      <c r="G24" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>16,6 (16,1–17,2)</v>
+      </c>
+      <c r="H24" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>15,3 (14,2–16,3)</v>
+      </c>
+      <c r="I24" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>0,031*</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B36" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="28" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
         <v>269</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B38" t="s">
+        <v>278</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="G38" t="s">
+        <v>204</v>
+      </c>
+      <c r="H38" t="s">
+        <v>203</v>
+      </c>
+      <c r="I38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="G39">
+        <f>IF(I39&lt;0.001,"&lt; 0.001*",IF(I39&lt;0.05,CONCATENATE(ROUND(I39,3),"*"),ROUND(I39,3)))</f>
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="H39">
+        <v>0.35</v>
+      </c>
+      <c r="I39">
+        <v>0.72719999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A40">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="G40">
+        <f>IF(I40&lt;0.001,"&lt; 0.001*",IF(I40&lt;0.05,CONCATENATE(ROUND(I40,3),"*"),ROUND(I40,3)))</f>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="H40">
+        <v>1.18</v>
+      </c>
+      <c r="I40">
+        <v>0.24299999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="G41">
+        <f>IF(I41&lt;0.001,"&lt; 0.001*",IF(I41&lt;0.05,CONCATENATE(ROUND(I41,3),"*"),ROUND(I41,3)))</f>
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="H41">
+        <v>0.95</v>
+      </c>
+      <c r="I41">
+        <v>0.34920000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="G42">
+        <f>IF(I42&lt;0.001,"&lt; 0.001*",IF(I42&lt;0.05,CONCATENATE(ROUND(I42,3),"*"),ROUND(I42,3)))</f>
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="H42">
+        <v>1.5</v>
+      </c>
+      <c r="I42">
+        <v>0.13880000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="G43">
+        <f>IF(I43&lt;0.001,"&lt; 0.001*",IF(I43&lt;0.05,CONCATENATE(ROUND(I43,3),"*"),ROUND(I43,3)))</f>
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="H43">
+        <v>-0.46</v>
+      </c>
+      <c r="I43">
+        <v>0.64490000000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A44">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="G44">
+        <f>IF(I44&lt;0.001,"&lt; 0.001*",IF(I44&lt;0.05,CONCATENATE(ROUND(I44,3),"*"),ROUND(I44,3)))</f>
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="H44">
+        <v>0.93</v>
+      </c>
+      <c r="I44">
+        <v>0.35370000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A45">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="E45" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14">
-        <v>6</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="22" t="s">
+      <c r="F45" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="15">
-        <v>0.35</v>
-      </c>
-      <c r="G4">
-        <f>IF(H4&lt;0.001,"&lt; 0.001*",IF(H4&lt;0.05,CONCATENATE(ROUND(H4,3),"*"),ROUND(H4,3)))</f>
-        <v>0.72699999999999998</v>
-      </c>
-      <c r="H4" s="16">
-        <v>0.72719999999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A5" s="17">
-        <v>5</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="23" t="s">
+      <c r="G45">
+        <f>IF(I45&lt;0.001,"&lt; 0.001*",IF(I45&lt;0.05,CONCATENATE(ROUND(I45,3),"*"),ROUND(I45,3)))</f>
+        <v>0.185</v>
+      </c>
+      <c r="H45">
+        <v>-1.34</v>
+      </c>
+      <c r="I45">
+        <v>0.18479999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A46">
+        <v>8</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D46" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E46" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="G46">
+        <f>IF(I46&lt;0.001,"&lt; 0.001*",IF(I46&lt;0.05,CONCATENATE(ROUND(I46,3),"*"),ROUND(I46,3)))</f>
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="H46">
+        <v>0.02</v>
+      </c>
+      <c r="I46">
+        <v>0.98760000000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A47">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="G47">
+        <f>IF(I47&lt;0.001,"&lt; 0.001*",IF(I47&lt;0.05,CONCATENATE(ROUND(I47,3),"*"),ROUND(I47,3)))</f>
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="H47">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="I47">
+        <v>0.57089999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A48">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="G48">
+        <f>IF(I48&lt;0.001,"&lt; 0.001*",IF(I48&lt;0.05,CONCATENATE(ROUND(I48,3),"*"),ROUND(I48,3)))</f>
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="H48">
+        <v>0.17</v>
+      </c>
+      <c r="I48">
+        <v>0.86850000000000005</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A49">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="G49">
+        <f>IF(I49&lt;0.001,"&lt; 0.001*",IF(I49&lt;0.05,CONCATENATE(ROUND(I49,3),"*"),ROUND(I49,3)))</f>
+        <v>6.2E-2</v>
+      </c>
+      <c r="H49">
+        <v>-1.91</v>
+      </c>
+      <c r="I49">
+        <v>6.1499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A50">
+        <v>16</v>
+      </c>
+      <c r="B50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="G50">
+        <f>IF(I50&lt;0.001,"&lt; 0.001*",IF(I50&lt;0.05,CONCATENATE(ROUND(I50,3),"*"),ROUND(I50,3)))</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="H50">
+        <v>-0.27</v>
+      </c>
+      <c r="I50">
+        <v>0.78510000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A51">
+        <v>17</v>
+      </c>
+      <c r="B51" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="G51" t="str">
+        <f>IF(I51&lt;0.001,"&lt; 0.001*",IF(I51&lt;0.05,CONCATENATE(ROUND(I51,3),"*"),ROUND(I51,3)))</f>
+        <v>0.025*</v>
+      </c>
+      <c r="H51">
+        <v>2.31</v>
+      </c>
+      <c r="I51">
+        <v>2.46E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A52">
+        <v>18</v>
+      </c>
+      <c r="B52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="G52" t="str">
+        <f>IF(I52&lt;0.001,"&lt; 0.001*",IF(I52&lt;0.05,CONCATENATE(ROUND(I52,3),"*"),ROUND(I52,3)))</f>
+        <v>0.016*</v>
+      </c>
+      <c r="H52">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="I52">
+        <v>1.6400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A53">
+        <v>19</v>
+      </c>
+      <c r="B53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="G53">
+        <f>IF(I53&lt;0.001,"&lt; 0.001*",IF(I53&lt;0.05,CONCATENATE(ROUND(I53,3),"*"),ROUND(I53,3)))</f>
+        <v>6.2E-2</v>
+      </c>
+      <c r="H53">
+        <v>1.91</v>
+      </c>
+      <c r="I53">
+        <v>6.1499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A54">
+        <v>20</v>
+      </c>
+      <c r="B54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="G54">
+        <f>IF(I54&lt;0.001,"&lt; 0.001*",IF(I54&lt;0.05,CONCATENATE(ROUND(I54,3),"*"),ROUND(I54,3)))</f>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="H54">
+        <v>1.96</v>
+      </c>
+      <c r="I54">
+        <v>5.4300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A55">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="G55" t="str">
+        <f>IF(I55&lt;0.001,"&lt; 0.001*",IF(I55&lt;0.05,CONCATENATE(ROUND(I55,3),"*"),ROUND(I55,3)))</f>
+        <v>0.044*</v>
+      </c>
+      <c r="H55">
+        <v>2.06</v>
+      </c>
+      <c r="I55">
+        <v>4.4299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A56">
+        <v>22</v>
+      </c>
+      <c r="B56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="F56" s="28" t="s">
+        <v>352</v>
+      </c>
+      <c r="G56">
+        <f>IF(I56&lt;0.001,"&lt; 0.001*",IF(I56&lt;0.05,CONCATENATE(ROUND(I56,3),"*"),ROUND(I56,3)))</f>
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="H56">
+        <v>1.41</v>
+      </c>
+      <c r="I56">
+        <v>0.1646</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A57">
+        <v>23</v>
+      </c>
+      <c r="B57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>355</v>
+      </c>
+      <c r="G57">
+        <f>IF(I57&lt;0.001,"&lt; 0.001*",IF(I57&lt;0.05,CONCATENATE(ROUND(I57,3),"*"),ROUND(I57,3)))</f>
+        <v>0.3</v>
+      </c>
+      <c r="H57">
+        <v>1.04</v>
+      </c>
+      <c r="I57">
+        <v>0.3004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A58">
+        <v>24</v>
+      </c>
+      <c r="B58" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>357</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="G58">
+        <f>IF(I58&lt;0.001,"&lt; 0.001*",IF(I58&lt;0.05,CONCATENATE(ROUND(I58,3),"*"),ROUND(I58,3)))</f>
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="H58">
+        <v>1.6</v>
+      </c>
+      <c r="I58">
+        <v>0.11650000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A59">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="F59" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="G59">
+        <f>IF(I59&lt;0.001,"&lt; 0.001*",IF(I59&lt;0.05,CONCATENATE(ROUND(I59,3),"*"),ROUND(I59,3)))</f>
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H59">
+        <v>1.66</v>
+      </c>
+      <c r="I59">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A60">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="E60" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="G60" t="str">
+        <f>IF(I60&lt;0.001,"&lt; 0.001*",IF(I60&lt;0.05,CONCATENATE(ROUND(I60,3),"*"),ROUND(I60,3)))</f>
+        <v>0.024*</v>
+      </c>
+      <c r="H60">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="I60">
+        <v>2.4199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A61">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="F61" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="G61" t="str">
+        <f>IF(I61&lt;0.001,"&lt; 0.001*",IF(I61&lt;0.05,CONCATENATE(ROUND(I61,3),"*"),ROUND(I61,3)))</f>
+        <v>0.031*</v>
+      </c>
+      <c r="H61">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="I61">
+        <v>3.0700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A67">
+        <v>10</v>
+      </c>
+      <c r="B67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" t="s">
+        <v>271</v>
+      </c>
+      <c r="E67" t="s">
         <v>274</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="F5" s="18">
-        <v>1.18</v>
-      </c>
-      <c r="G5">
-        <f t="shared" ref="G4:G15" si="0">IF(H5&lt;0.001,"&lt; 0.001*",IF(H5&lt;0.05,CONCATENATE(ROUND(H5,3),"*"),ROUND(H5,3)))</f>
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="H5" s="19">
-        <v>0.24299999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A6" s="17">
-        <v>9</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="F6" s="18">
-        <v>0.95</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="H6" s="19">
-        <v>0.34920000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A7" s="14">
-        <v>2</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="F7" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="H7" s="19">
-        <v>0.13880000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A8" s="17">
-        <v>3</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="G67">
+        <f>IF(I67&lt;0.05,CONCATENATE(ROUND(I67,3),"*"),ROUND(I67,3))</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="H67">
+        <v>-0.46</v>
+      </c>
+      <c r="I67">
+        <v>0.64359999999999995</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A68">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" t="s">
+        <v>272</v>
+      </c>
+      <c r="E68" t="s">
+        <v>151</v>
+      </c>
+      <c r="G68">
+        <f>IF(I68&lt;0.05,CONCATENATE(ROUND(I68,3),"*"),ROUND(I68,3))</f>
+        <v>0.99</v>
+      </c>
+      <c r="H68">
+        <v>0.01</v>
+      </c>
+      <c r="I68">
+        <v>0.98980000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A69">
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" t="s">
+        <v>273</v>
+      </c>
+      <c r="E69" t="s">
         <v>275</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="15">
-        <v>-0.46</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="H8" s="16">
-        <v>0.64490000000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A9" s="14">
-        <v>4</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="F9" s="15">
-        <v>0.93</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="H9" s="16">
-        <v>0.35370000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A10" s="17">
-        <v>7</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="F10" s="18">
-        <v>-1.34</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>0.185</v>
-      </c>
-      <c r="H10" s="19">
-        <v>0.18479999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A11" s="14">
-        <v>8</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="F11" s="15">
-        <v>0.02</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.98760000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A12" s="17">
-        <v>13</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="F12" s="18">
-        <v>-0.56999999999999995</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>0.57099999999999995</v>
-      </c>
-      <c r="H12" s="19">
-        <v>0.57089999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A13" s="14">
-        <v>14</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="F13" s="15">
-        <v>0.17</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
-        <v>0.86899999999999999</v>
-      </c>
-      <c r="H13" s="16">
-        <v>0.86850000000000005</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A14" s="17">
-        <v>15</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="F14" s="18">
-        <v>-1.91</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>6.2E-2</v>
-      </c>
-      <c r="H14" s="19">
-        <v>6.1499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A15" s="14">
-        <v>16</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="F15" s="18">
-        <v>-0.27</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-      <c r="H15" s="19">
-        <v>0.78510000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A16" s="17">
-        <v>17</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="F16" s="15">
-        <v>2.31</v>
-      </c>
-      <c r="G16" t="str">
-        <f>IF(H16&lt;0.001,"&lt; 0.001*",IF(H16&lt;0.05,CONCATENATE(ROUND(H16,3),"*"),ROUND(H16,3)))</f>
-        <v>0.025*</v>
-      </c>
-      <c r="H16" s="16">
-        <v>2.46E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A17" s="14">
-        <v>18</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="F17" s="18">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="G17" t="str">
-        <f t="shared" ref="G17:G26" si="1">IF(H17&lt;0.001,"&lt; 0.001*",IF(H17&lt;0.05,CONCATENATE(ROUND(H17,3),"*"),ROUND(H17,3)))</f>
-        <v>0.016*</v>
-      </c>
-      <c r="H17" s="19">
-        <v>1.6400000000000001E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A18" s="17">
-        <v>19</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="F18" s="15">
-        <v>1.91</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>6.2E-2</v>
-      </c>
-      <c r="H18" s="16">
-        <v>6.1499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A19" s="14">
-        <v>20</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="F19" s="18">
-        <v>1.96</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="H19" s="19">
-        <v>5.4300000000000001E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A20" s="17">
-        <v>21</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="F20" s="15">
-        <v>2.06</v>
-      </c>
-      <c r="G20" t="str">
-        <f t="shared" si="1"/>
-        <v>0.044*</v>
-      </c>
-      <c r="H20" s="16">
-        <v>4.4299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A21" s="14">
-        <v>22</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>337</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="F21" s="18">
-        <v>1.41</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="H21" s="19">
-        <v>0.1646</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A22" s="17">
-        <v>23</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="F22" s="15">
-        <v>1.04</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>0.3</v>
-      </c>
-      <c r="H22" s="16">
-        <v>0.3004</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A23" s="14">
-        <v>24</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="F23" s="18">
-        <v>1.6</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="H23" s="19">
-        <v>0.11650000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A24" s="17">
-        <v>25</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="F24" s="15">
-        <v>1.66</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="1"/>
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="H24" s="16">
-        <v>0.10199999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A25" s="14">
-        <v>26</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>315</v>
-      </c>
-      <c r="F25" s="15">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="1"/>
-        <v>0.024*</v>
-      </c>
-      <c r="H25" s="16">
-        <v>2.4199999999999999E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>27</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F26" s="9">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="G26" t="str">
-        <f t="shared" si="1"/>
-        <v>0.031*</v>
-      </c>
-      <c r="H26" s="10">
-        <v>3.0700000000000002E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A32" s="14">
-        <v>10</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="F32" s="15">
-        <v>-0.46</v>
-      </c>
-      <c r="G32" s="7">
-        <f>IF(H32&lt;0.05,CONCATENATE(ROUND(H32,3),"*"),ROUND(H32,3))</f>
-        <v>0.64400000000000002</v>
-      </c>
-      <c r="H32" s="16">
-        <v>0.64359999999999995</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A33" s="17">
-        <v>11</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="F33" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="G33" s="7">
-        <f>IF(H33&lt;0.05,CONCATENATE(ROUND(H33,3),"*"),ROUND(H33,3))</f>
-        <v>0.99</v>
-      </c>
-      <c r="H33" s="19">
-        <v>0.98980000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A34" s="14">
-        <v>12</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="F34" s="15">
+      <c r="G69">
+        <f>IF(I69&lt;0.05,CONCATENATE(ROUND(I69,3),"*"),ROUND(I69,3))</f>
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="H69">
         <v>-0.36</v>
       </c>
-      <c r="G34" s="7">
-        <f>IF(H34&lt;0.05,CONCATENATE(ROUND(H34,3),"*"),ROUND(H34,3))</f>
-        <v>0.71899999999999997</v>
-      </c>
-      <c r="H34" s="16">
+      <c r="I69">
         <v>0.71919999999999995</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>0.05</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Output/Baseline/Data_files/bia_baseline.xlsx
+++ b/Output/Baseline/Data_files/bia_baseline.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gustavosplmoura/Library/Mobile Documents/com~apple~CloudDocs/Medicina/Biblioteca/Research/Data Science/Data Science/PROJECTS/DVEP/Output/Baseline/Data_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gustavosplmoura/Library/Mobile Documents/com~apple~CloudDocs/Medicina/Biblioteca/Research/Data Science/DVEP/Output/Baseline/Data_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E9FAAB-BE70-6841-A9DC-0103A567DE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6121E7-ABD7-5041-894A-A2311AAE9098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="1440" windowWidth="28580" windowHeight="23700" activeTab="3" xr2:uid="{FD799774-BD8C-8548-A615-459C767A3F24}"/>
+    <workbookView xWindow="12540" yWindow="1440" windowWidth="28580" windowHeight="23700" activeTab="2" xr2:uid="{FD799774-BD8C-8548-A615-459C767A3F24}"/>
   </bookViews>
   <sheets>
     <sheet name="bia_baseline" sheetId="1" r:id="rId1"/>
     <sheet name="by sex" sheetId="2" r:id="rId2"/>
-    <sheet name="males, by group" sheetId="3" r:id="rId3"/>
-    <sheet name="females, by group" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="males, by group" sheetId="3" r:id="rId4"/>
+    <sheet name="females, by group" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="394">
   <si>
     <t>record_id</t>
   </si>
@@ -1144,6 +1145,84 @@
   </si>
   <si>
     <t>0,031*</t>
+  </si>
+  <si>
+    <t>Ângulo de Fase</t>
+  </si>
+  <si>
+    <t>Média de Resistência</t>
+  </si>
+  <si>
+    <t>Média de Reatância</t>
+  </si>
+  <si>
+    <t>Nível de Atividade Física</t>
+  </si>
+  <si>
+    <t>Índice de Massa Corporal</t>
+  </si>
+  <si>
+    <t>Gasto Energético Total</t>
+  </si>
+  <si>
+    <t>Gasto Energético em Repouso</t>
+  </si>
+  <si>
+    <t>Energia Armazenada</t>
+  </si>
+  <si>
+    <t>Massa de Gordura Absoluta</t>
+  </si>
+  <si>
+    <t>Índice de Massa de Gordura</t>
+  </si>
+  <si>
+    <t>Massa de Gordura Relativa</t>
+  </si>
+  <si>
+    <t>Massa Livre de Gordura Absoluta</t>
+  </si>
+  <si>
+    <t>Índice de Massa Livre de Gordura</t>
+  </si>
+  <si>
+    <t>Massa Livre de Gordura Relativa</t>
+  </si>
+  <si>
+    <t>Massa Muscular Esquelética do Corpo</t>
+  </si>
+  <si>
+    <t>Massa Muscular Esquelética do Tronco</t>
+  </si>
+  <si>
+    <t>Massa Muscular Esquelética do Braço Direito</t>
+  </si>
+  <si>
+    <t>Massa Muscular Esquelética do Braço Esquerdo</t>
+  </si>
+  <si>
+    <t>Massa Muscular Esquelética da Perna Direita</t>
+  </si>
+  <si>
+    <t>Massa Muscular Esquelética da Perna Esquerda</t>
+  </si>
+  <si>
+    <t>Tecido Adiposo Visceral</t>
+  </si>
+  <si>
+    <t>Água Corporal Total</t>
+  </si>
+  <si>
+    <t>Água Extracelular</t>
+  </si>
+  <si>
+    <t>Gasto Energético Total (kcal)</t>
+  </si>
+  <si>
+    <t>Gasto Energético em Repouso (kcal)</t>
+  </si>
+  <si>
+    <t>Energia Armazenada (kcal)</t>
   </si>
 </sst>
 </file>
@@ -1826,7 +1905,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1870,12 +1949,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1921,17 +2006,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8984,7 +9059,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF158CB-E912-B44A-B12F-04C4E260788C}">
-  <dimension ref="B1:K33"/>
+  <dimension ref="B1:K66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -9640,7 +9715,7 @@
       </c>
       <c r="K32" s="15"/>
     </row>
-    <row r="33" spans="3:11" ht="14" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:11" ht="14" x14ac:dyDescent="0.15">
       <c r="C33" t="s">
         <v>152</v>
       </c>
@@ -9662,9 +9737,140 @@
       </c>
       <c r="K33" s="15"/>
     </row>
+    <row r="40" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="32" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="B42" s="33" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="B43" s="33" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="B44" s="33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="B45" s="33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="B46" s="33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="B47" s="33" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="B48" s="33" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B49" s="33" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B50" s="33" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B51" s="33" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B52" s="33" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B53" s="33" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B54" s="33" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B55" s="33" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B56" s="33" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B57" s="33" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B58" s="33" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B59" s="33" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B60" s="33" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B61" s="33" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B62" s="33" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="30" x14ac:dyDescent="0.15">
+      <c r="B63" s="33" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B64" s="33" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B65" s="33" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="15" x14ac:dyDescent="0.15">
+      <c r="B66" s="33" t="s">
+        <v>390</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="G1:H1 H1:H1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9673,11 +9879,241 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5DAF801-242F-3E41-9833-48352AD5A73F}">
+  <dimension ref="B1:C27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="32.5" style="34" customWidth="1"/>
+    <col min="2" max="2" width="31" style="34" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" style="34" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="34" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B3" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B4" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B5" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B8" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B9" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B10" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B11" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B12" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B13" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B14" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B15" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B16" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B17" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B18" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B19" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B20" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B21" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B22" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B23" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B25" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B26" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B27" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>393</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE52CD2-C5A8-4E4A-B8BB-052C688E70B9}">
   <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="27.6640625" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" style="3"/>
@@ -10421,7 +10857,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10430,7 +10866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFB1076-8356-7A4B-BA71-77A67C3F751C}">
   <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -10455,21 +10891,21 @@
       <c r="D1" t="s">
         <v>204</v>
       </c>
-      <c r="F1" s="32" t="str">
+      <c r="F1" s="31" t="str">
         <f>TRIM(A1)</f>
         <v>Parâmetro</v>
       </c>
-      <c r="G1" s="32" t="str">
+      <c r="G1" s="31" t="str">
         <f t="shared" ref="G1:I16" si="0">TRIM(B1)</f>
         <v>Grupo placebo
 média (IC 95%)</v>
       </c>
-      <c r="H1" s="32" t="str">
+      <c r="H1" s="31" t="str">
         <f t="shared" si="0"/>
         <v>Grupo Eclipta
 média (IC 95%)</v>
       </c>
-      <c r="I1" s="32" t="str">
+      <c r="I1" s="31" t="str">
         <f t="shared" si="0"/>
         <v>Valor p</v>
       </c>
@@ -10487,19 +10923,19 @@
       <c r="D2" t="s">
         <v>303</v>
       </c>
-      <c r="F2" s="32" t="str">
+      <c r="F2" s="31" t="str">
         <f t="shared" ref="F2:F24" si="1">TRIM(A2)</f>
         <v>Altura (m)</v>
       </c>
-      <c r="G2" s="32" t="str">
+      <c r="G2" s="31" t="str">
         <f t="shared" si="0"/>
         <v>1,6 (1,6–1,7)</v>
       </c>
-      <c r="H2" s="32" t="str">
+      <c r="H2" s="31" t="str">
         <f t="shared" si="0"/>
         <v>1,6 (1,6–1,7)</v>
       </c>
-      <c r="I2" s="32" t="str">
+      <c r="I2" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,727</v>
       </c>
@@ -10517,19 +10953,19 @@
       <c r="D3" t="s">
         <v>306</v>
       </c>
-      <c r="F3" s="32" t="str">
+      <c r="F3" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Peso (kg)</v>
       </c>
-      <c r="G3" s="32" t="str">
+      <c r="G3" s="31" t="str">
         <f t="shared" si="0"/>
         <v>92 (87,5–96,4)</v>
       </c>
-      <c r="H3" s="32" t="str">
+      <c r="H3" s="31" t="str">
         <f t="shared" si="0"/>
         <v>88,7 (85,7–91,7)</v>
       </c>
-      <c r="I3" s="32" t="str">
+      <c r="I3" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,243</v>
       </c>
@@ -10547,19 +10983,19 @@
       <c r="D4" t="s">
         <v>309</v>
       </c>
-      <c r="F4" s="32" t="str">
+      <c r="F4" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Índice de Massa Corporal (kg/m²)</v>
       </c>
-      <c r="G4" s="32" t="str">
+      <c r="G4" s="31" t="str">
         <f t="shared" si="0"/>
         <v>35,2 (31–39,4)</v>
       </c>
-      <c r="H4" s="32" t="str">
+      <c r="H4" s="31" t="str">
         <f t="shared" si="0"/>
         <v>33,1 (32,4–33,9)</v>
       </c>
-      <c r="I4" s="32" t="str">
+      <c r="I4" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,349</v>
       </c>
@@ -10577,19 +11013,19 @@
       <c r="D5" t="s">
         <v>311</v>
       </c>
-      <c r="F5" s="32" t="str">
+      <c r="F5" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Circunferência Abdominal (m)</v>
       </c>
-      <c r="G5" s="32" t="str">
+      <c r="G5" s="31" t="str">
         <f t="shared" si="0"/>
         <v>1 (1–1)</v>
       </c>
-      <c r="H5" s="32" t="str">
+      <c r="H5" s="31" t="str">
         <f t="shared" si="0"/>
         <v>1 (0,9–1)</v>
       </c>
-      <c r="I5" s="32" t="str">
+      <c r="I5" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,139</v>
       </c>
@@ -10607,19 +11043,19 @@
       <c r="D6" t="s">
         <v>314</v>
       </c>
-      <c r="F6" s="32" t="str">
+      <c r="F6" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Nível de Atividade Física (PAL)</v>
       </c>
-      <c r="G6" s="32" t="str">
+      <c r="G6" s="31" t="str">
         <f t="shared" si="0"/>
         <v>1,3 (1,3–1,4)</v>
       </c>
-      <c r="H6" s="32" t="str">
+      <c r="H6" s="31" t="str">
         <f t="shared" si="0"/>
         <v>1,4 (1,3–1,4)</v>
       </c>
-      <c r="I6" s="32" t="str">
+      <c r="I6" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,645</v>
       </c>
@@ -10637,19 +11073,19 @@
       <c r="D7" t="s">
         <v>317</v>
       </c>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Ângulo de Fase (°)</v>
       </c>
-      <c r="G7" s="32" t="str">
+      <c r="G7" s="31" t="str">
         <f t="shared" si="0"/>
         <v>6,5 (6,1–6,8)</v>
       </c>
-      <c r="H7" s="32" t="str">
+      <c r="H7" s="31" t="str">
         <f t="shared" si="0"/>
         <v>6,3 (5,9–6,6)</v>
       </c>
-      <c r="I7" s="32" t="str">
+      <c r="I7" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,354</v>
       </c>
@@ -10667,19 +11103,19 @@
       <c r="D8" t="s">
         <v>320</v>
       </c>
-      <c r="F8" s="32" t="str">
+      <c r="F8" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Resistência (Ω)</v>
       </c>
-      <c r="G8" s="32" t="str">
+      <c r="G8" s="31" t="str">
         <f t="shared" si="0"/>
         <v>538,2 (519,3–557)</v>
       </c>
-      <c r="H8" s="32" t="str">
+      <c r="H8" s="31" t="str">
         <f t="shared" si="0"/>
         <v>556,6 (537,3–575,9)</v>
       </c>
-      <c r="I8" s="32" t="str">
+      <c r="I8" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,185</v>
       </c>
@@ -10697,19 +11133,19 @@
       <c r="D9" t="s">
         <v>323</v>
       </c>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Reatância (Ω)</v>
       </c>
-      <c r="G9" s="32" t="str">
+      <c r="G9" s="31" t="str">
         <f t="shared" si="0"/>
         <v>60,8 (57,8–63,8)</v>
       </c>
-      <c r="H9" s="32" t="str">
+      <c r="H9" s="31" t="str">
         <f t="shared" si="0"/>
         <v>60,8 (57,5–64,1)</v>
       </c>
-      <c r="I9" s="32" t="str">
+      <c r="I9" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,988</v>
       </c>
@@ -10727,19 +11163,19 @@
       <c r="D10" t="s">
         <v>326</v>
       </c>
-      <c r="F10" s="32" t="str">
+      <c r="F10" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Massa gorda Absoluta (kg)</v>
       </c>
-      <c r="G10" s="32" t="str">
+      <c r="G10" s="31" t="str">
         <f t="shared" si="0"/>
         <v>41,6 (37,6–45,6)</v>
       </c>
-      <c r="H10" s="32" t="str">
+      <c r="H10" s="31" t="str">
         <f t="shared" si="0"/>
         <v>43,1 (40–46,1)</v>
       </c>
-      <c r="I10" s="32" t="str">
+      <c r="I10" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,571</v>
       </c>
@@ -10757,19 +11193,19 @@
       <c r="D11" t="s">
         <v>329</v>
       </c>
-      <c r="F11" s="32" t="str">
+      <c r="F11" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Índice de Massa gorda (kg/m²)</v>
       </c>
-      <c r="G11" s="32" t="str">
+      <c r="G11" s="31" t="str">
         <f t="shared" si="0"/>
         <v>16,5 (12,7–20,2)</v>
       </c>
-      <c r="H11" s="32" t="str">
+      <c r="H11" s="31" t="str">
         <f t="shared" si="0"/>
         <v>16,1 (14,9–17,3)</v>
       </c>
-      <c r="I11" s="32" t="str">
+      <c r="I11" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,869</v>
       </c>
@@ -10787,19 +11223,19 @@
       <c r="D12" t="s">
         <v>332</v>
       </c>
-      <c r="F12" s="32" t="str">
+      <c r="F12" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Massa gorda Relativa (%)</v>
       </c>
-      <c r="G12" s="32" t="str">
+      <c r="G12" s="31" t="str">
         <f t="shared" si="0"/>
         <v>44,7 (42,6–46,8)</v>
       </c>
-      <c r="H12" s="32" t="str">
+      <c r="H12" s="31" t="str">
         <f t="shared" si="0"/>
         <v>48,6 (45,2–52,1)</v>
       </c>
-      <c r="I12" s="32" t="str">
+      <c r="I12" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,062</v>
       </c>
@@ -10817,19 +11253,19 @@
       <c r="D13" t="s">
         <v>335</v>
       </c>
-      <c r="F13" s="32" t="str">
+      <c r="F13" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Tecido Adiposo Visceral (kg)</v>
       </c>
-      <c r="G13" s="32" t="str">
+      <c r="G13" s="31" t="str">
         <f t="shared" si="0"/>
         <v>2,2 (1,9–2,5)</v>
       </c>
-      <c r="H13" s="32" t="str">
+      <c r="H13" s="31" t="str">
         <f t="shared" si="0"/>
         <v>2,3 (2–2,5)</v>
       </c>
-      <c r="I13" s="32" t="str">
+      <c r="I13" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,785</v>
       </c>
@@ -10847,19 +11283,19 @@
       <c r="D14" t="s">
         <v>338</v>
       </c>
-      <c r="F14" s="32" t="str">
+      <c r="F14" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Massa Livre de Gordura Absoluta (kg)</v>
       </c>
-      <c r="G14" s="32" t="str">
+      <c r="G14" s="31" t="str">
         <f t="shared" si="0"/>
         <v>50,4 (48,1–52,7)</v>
       </c>
-      <c r="H14" s="32" t="str">
+      <c r="H14" s="31" t="str">
         <f t="shared" si="0"/>
         <v>45,6 (42,4–48,9)</v>
       </c>
-      <c r="I14" s="32" t="str">
+      <c r="I14" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,025*</v>
       </c>
@@ -10877,19 +11313,19 @@
       <c r="D15" t="s">
         <v>341</v>
       </c>
-      <c r="F15" s="32" t="str">
+      <c r="F15" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Índice de Massa Livre de Gordura (kg/m²)</v>
       </c>
-      <c r="G15" s="32" t="str">
+      <c r="G15" s="31" t="str">
         <f t="shared" si="0"/>
         <v>18,7 (18–19,5)</v>
       </c>
-      <c r="H15" s="32" t="str">
+      <c r="H15" s="31" t="str">
         <f t="shared" si="0"/>
         <v>17 (15,9–18,2)</v>
       </c>
-      <c r="I15" s="32" t="str">
+      <c r="I15" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,016*</v>
       </c>
@@ -10907,19 +11343,19 @@
       <c r="D16" t="s">
         <v>332</v>
       </c>
-      <c r="F16" s="32" t="str">
+      <c r="F16" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Massa Livre de Gordura Relativa (%)</v>
       </c>
-      <c r="G16" s="32" t="str">
+      <c r="G16" s="31" t="str">
         <f t="shared" si="0"/>
         <v>55,3 (53,2–57,4)</v>
       </c>
-      <c r="H16" s="32" t="str">
+      <c r="H16" s="31" t="str">
         <f t="shared" si="0"/>
         <v>51,4 (47,9–54,8)</v>
       </c>
-      <c r="I16" s="32" t="str">
+      <c r="I16" s="31" t="str">
         <f t="shared" si="0"/>
         <v>0,062</v>
       </c>
@@ -10937,19 +11373,19 @@
       <c r="D17" t="s">
         <v>346</v>
       </c>
-      <c r="F17" s="32" t="str">
+      <c r="F17" s="31" t="str">
         <f t="shared" si="1"/>
         <v>MME Corporal Total (kg)</v>
       </c>
-      <c r="G17" s="32" t="str">
+      <c r="G17" s="31" t="str">
         <f t="shared" ref="G17:G24" si="2">TRIM(B17)</f>
         <v>24,4 (23–25,8)</v>
       </c>
-      <c r="H17" s="32" t="str">
+      <c r="H17" s="31" t="str">
         <f t="shared" ref="H17:H24" si="3">TRIM(C17)</f>
         <v>21,9 (19,9–24)</v>
       </c>
-      <c r="I17" s="32" t="str">
+      <c r="I17" s="31" t="str">
         <f t="shared" ref="I17:I24" si="4">TRIM(D17)</f>
         <v>0,054</v>
       </c>
@@ -10967,19 +11403,19 @@
       <c r="D18" t="s">
         <v>349</v>
       </c>
-      <c r="F18" s="32" t="str">
+      <c r="F18" s="31" t="str">
         <f t="shared" si="1"/>
         <v>MME do Tronco (kg)</v>
       </c>
-      <c r="G18" s="32" t="str">
+      <c r="G18" s="31" t="str">
         <f t="shared" si="2"/>
         <v>11,1 (10,3–11,8)</v>
       </c>
-      <c r="H18" s="32" t="str">
+      <c r="H18" s="31" t="str">
         <f t="shared" si="3"/>
         <v>9,7 (8,6–10,8)</v>
       </c>
-      <c r="I18" s="32" t="str">
+      <c r="I18" s="31" t="str">
         <f t="shared" si="4"/>
         <v>0,044*</v>
       </c>
@@ -10997,19 +11433,19 @@
       <c r="D19" t="s">
         <v>352</v>
       </c>
-      <c r="F19" s="32" t="str">
+      <c r="F19" s="31" t="str">
         <f t="shared" si="1"/>
         <v>MME do Braço Direito (kg)</v>
       </c>
-      <c r="G19" s="32" t="str">
+      <c r="G19" s="31" t="str">
         <f t="shared" si="2"/>
         <v>1,4 (1,2–1,5)</v>
       </c>
-      <c r="H19" s="32" t="str">
+      <c r="H19" s="31" t="str">
         <f t="shared" si="3"/>
         <v>1,3 (1,2–1,3)</v>
       </c>
-      <c r="I19" s="32" t="str">
+      <c r="I19" s="31" t="str">
         <f t="shared" si="4"/>
         <v>0,165</v>
       </c>
@@ -11027,19 +11463,19 @@
       <c r="D20" t="s">
         <v>355</v>
       </c>
-      <c r="F20" s="32" t="str">
+      <c r="F20" s="31" t="str">
         <f t="shared" si="1"/>
         <v>MME do Braço Esquerdo (kg)</v>
       </c>
-      <c r="G20" s="32" t="str">
+      <c r="G20" s="31" t="str">
         <f t="shared" si="2"/>
         <v>1,3 (1,2–1,5)</v>
       </c>
-      <c r="H20" s="32" t="str">
+      <c r="H20" s="31" t="str">
         <f t="shared" si="3"/>
         <v>1,3 (1,1–1,4)</v>
       </c>
-      <c r="I20" s="32" t="str">
+      <c r="I20" s="31" t="str">
         <f t="shared" si="4"/>
         <v>0,3</v>
       </c>
@@ -11057,19 +11493,19 @@
       <c r="D21" t="s">
         <v>358</v>
       </c>
-      <c r="F21" s="32" t="str">
+      <c r="F21" s="31" t="str">
         <f t="shared" si="1"/>
         <v>MME da Perna Direita (kg)</v>
       </c>
-      <c r="G21" s="32" t="str">
+      <c r="G21" s="31" t="str">
         <f t="shared" si="2"/>
         <v>5,2 (4,9–5,4)</v>
       </c>
-      <c r="H21" s="32" t="str">
+      <c r="H21" s="31" t="str">
         <f t="shared" si="3"/>
         <v>4,8 (4,3–5,2)</v>
       </c>
-      <c r="I21" s="32" t="str">
+      <c r="I21" s="31" t="str">
         <f t="shared" si="4"/>
         <v>0,117</v>
       </c>
@@ -11087,19 +11523,19 @@
       <c r="D22" t="s">
         <v>361</v>
       </c>
-      <c r="F22" s="32" t="str">
+      <c r="F22" s="31" t="str">
         <f t="shared" si="1"/>
         <v>MME da Perna Esquerda (kg)</v>
       </c>
-      <c r="G22" s="32" t="str">
+      <c r="G22" s="31" t="str">
         <f t="shared" si="2"/>
         <v>5,4 (5,1–5,7)</v>
       </c>
-      <c r="H22" s="32" t="str">
+      <c r="H22" s="31" t="str">
         <f t="shared" si="3"/>
         <v>4,9 (4,4–5,4)</v>
       </c>
-      <c r="I22" s="32" t="str">
+      <c r="I22" s="31" t="str">
         <f t="shared" si="4"/>
         <v>0,102</v>
       </c>
@@ -11117,19 +11553,19 @@
       <c r="D23" t="s">
         <v>364</v>
       </c>
-      <c r="F23" s="32" t="str">
+      <c r="F23" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Água Corporal Total (L)</v>
       </c>
-      <c r="G23" s="32" t="str">
+      <c r="G23" s="31" t="str">
         <f t="shared" si="2"/>
         <v>37,8 (36,2–39,4)</v>
       </c>
-      <c r="H23" s="32" t="str">
+      <c r="H23" s="31" t="str">
         <f t="shared" si="3"/>
         <v>34,2 (31,6–36,8)</v>
       </c>
-      <c r="I23" s="32" t="str">
+      <c r="I23" s="31" t="str">
         <f t="shared" si="4"/>
         <v>0,024*</v>
       </c>
@@ -11147,19 +11583,19 @@
       <c r="D24" t="s">
         <v>367</v>
       </c>
-      <c r="F24" s="32" t="str">
+      <c r="F24" s="31" t="str">
         <f t="shared" si="1"/>
         <v>Água Extracelular (L)</v>
       </c>
-      <c r="G24" s="32" t="str">
+      <c r="G24" s="31" t="str">
         <f t="shared" si="2"/>
         <v>16,6 (16,1–17,2)</v>
       </c>
-      <c r="H24" s="32" t="str">
+      <c r="H24" s="31" t="str">
         <f t="shared" si="3"/>
         <v>15,3 (14,2–16,3)</v>
       </c>
-      <c r="I24" s="32" t="str">
+      <c r="I24" s="31" t="str">
         <f t="shared" si="4"/>
         <v>0,031*</v>
       </c>
@@ -11169,7 +11605,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="28" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:9" ht="56" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>269</v>
       </c>
@@ -11208,17 +11644,17 @@
       <c r="C39" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" t="s">
         <v>302</v>
       </c>
-      <c r="E39" s="27" t="s">
+      <c r="E39" t="s">
         <v>302</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="27" t="s">
         <v>303</v>
       </c>
       <c r="G39">
-        <f>IF(I39&lt;0.001,"&lt; 0.001*",IF(I39&lt;0.05,CONCATENATE(ROUND(I39,3),"*"),ROUND(I39,3)))</f>
+        <f t="shared" ref="G39:G61" si="5">IF(I39&lt;0.001,"&lt; 0.001*",IF(I39&lt;0.05,CONCATENATE(ROUND(I39,3),"*"),ROUND(I39,3)))</f>
         <v>0.72699999999999998</v>
       </c>
       <c r="H39">
@@ -11238,17 +11674,17 @@
       <c r="C40" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" t="s">
         <v>304</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="E40" t="s">
         <v>305</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="27" t="s">
         <v>306</v>
       </c>
       <c r="G40">
-        <f>IF(I40&lt;0.001,"&lt; 0.001*",IF(I40&lt;0.05,CONCATENATE(ROUND(I40,3),"*"),ROUND(I40,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.24299999999999999</v>
       </c>
       <c r="H40">
@@ -11268,17 +11704,17 @@
       <c r="C41" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" t="s">
         <v>307</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" t="s">
         <v>308</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="27" t="s">
         <v>309</v>
       </c>
       <c r="G41">
-        <f>IF(I41&lt;0.001,"&lt; 0.001*",IF(I41&lt;0.05,CONCATENATE(ROUND(I41,3),"*"),ROUND(I41,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.34899999999999998</v>
       </c>
       <c r="H41">
@@ -11298,17 +11734,17 @@
       <c r="C42" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" t="s">
         <v>143</v>
       </c>
-      <c r="E42" s="27" t="s">
+      <c r="E42" t="s">
         <v>310</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="27" t="s">
         <v>311</v>
       </c>
       <c r="G42">
-        <f>IF(I42&lt;0.001,"&lt; 0.001*",IF(I42&lt;0.05,CONCATENATE(ROUND(I42,3),"*"),ROUND(I42,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.13900000000000001</v>
       </c>
       <c r="H42">
@@ -11328,17 +11764,17 @@
       <c r="C43" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" t="s">
         <v>312</v>
       </c>
-      <c r="E43" s="27" t="s">
+      <c r="E43" t="s">
         <v>313</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F43" s="27" t="s">
         <v>314</v>
       </c>
       <c r="G43">
-        <f>IF(I43&lt;0.001,"&lt; 0.001*",IF(I43&lt;0.05,CONCATENATE(ROUND(I43,3),"*"),ROUND(I43,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.64500000000000002</v>
       </c>
       <c r="H43">
@@ -11358,17 +11794,17 @@
       <c r="C44" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="D44" s="27" t="s">
+      <c r="D44" t="s">
         <v>315</v>
       </c>
-      <c r="E44" s="27" t="s">
+      <c r="E44" t="s">
         <v>316</v>
       </c>
-      <c r="F44" s="28" t="s">
+      <c r="F44" s="27" t="s">
         <v>317</v>
       </c>
       <c r="G44">
-        <f>IF(I44&lt;0.001,"&lt; 0.001*",IF(I44&lt;0.05,CONCATENATE(ROUND(I44,3),"*"),ROUND(I44,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.35399999999999998</v>
       </c>
       <c r="H44">
@@ -11388,17 +11824,17 @@
       <c r="C45" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D45" t="s">
         <v>318</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="E45" t="s">
         <v>319</v>
       </c>
-      <c r="F45" s="28" t="s">
+      <c r="F45" s="27" t="s">
         <v>320</v>
       </c>
       <c r="G45">
-        <f>IF(I45&lt;0.001,"&lt; 0.001*",IF(I45&lt;0.05,CONCATENATE(ROUND(I45,3),"*"),ROUND(I45,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.185</v>
       </c>
       <c r="H45">
@@ -11418,17 +11854,17 @@
       <c r="C46" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" t="s">
         <v>321</v>
       </c>
-      <c r="E46" s="27" t="s">
+      <c r="E46" t="s">
         <v>322</v>
       </c>
-      <c r="F46" s="28" t="s">
+      <c r="F46" s="27" t="s">
         <v>323</v>
       </c>
       <c r="G46">
-        <f>IF(I46&lt;0.001,"&lt; 0.001*",IF(I46&lt;0.05,CONCATENATE(ROUND(I46,3),"*"),ROUND(I46,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.98799999999999999</v>
       </c>
       <c r="H46">
@@ -11448,17 +11884,17 @@
       <c r="C47" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" t="s">
         <v>324</v>
       </c>
-      <c r="E47" s="27" t="s">
+      <c r="E47" t="s">
         <v>325</v>
       </c>
-      <c r="F47" s="28" t="s">
+      <c r="F47" s="27" t="s">
         <v>326</v>
       </c>
       <c r="G47">
-        <f>IF(I47&lt;0.001,"&lt; 0.001*",IF(I47&lt;0.05,CONCATENATE(ROUND(I47,3),"*"),ROUND(I47,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.57099999999999995</v>
       </c>
       <c r="H47">
@@ -11478,17 +11914,17 @@
       <c r="C48" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" t="s">
         <v>327</v>
       </c>
-      <c r="E48" s="27" t="s">
+      <c r="E48" t="s">
         <v>328</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F48" s="27" t="s">
         <v>329</v>
       </c>
       <c r="G48">
-        <f>IF(I48&lt;0.001,"&lt; 0.001*",IF(I48&lt;0.05,CONCATENATE(ROUND(I48,3),"*"),ROUND(I48,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.86899999999999999</v>
       </c>
       <c r="H48">
@@ -11508,17 +11944,17 @@
       <c r="C49" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="D49" s="27" t="s">
+      <c r="D49" t="s">
         <v>330</v>
       </c>
-      <c r="E49" s="27" t="s">
+      <c r="E49" t="s">
         <v>331</v>
       </c>
-      <c r="F49" s="28" t="s">
+      <c r="F49" s="27" t="s">
         <v>332</v>
       </c>
       <c r="G49">
-        <f>IF(I49&lt;0.001,"&lt; 0.001*",IF(I49&lt;0.05,CONCATENATE(ROUND(I49,3),"*"),ROUND(I49,3)))</f>
+        <f t="shared" si="5"/>
         <v>6.2E-2</v>
       </c>
       <c r="H49">
@@ -11538,17 +11974,17 @@
       <c r="C50" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" t="s">
         <v>333</v>
       </c>
-      <c r="E50" s="27" t="s">
+      <c r="E50" t="s">
         <v>334</v>
       </c>
-      <c r="F50" s="28" t="s">
+      <c r="F50" s="27" t="s">
         <v>335</v>
       </c>
       <c r="G50">
-        <f>IF(I50&lt;0.001,"&lt; 0.001*",IF(I50&lt;0.05,CONCATENATE(ROUND(I50,3),"*"),ROUND(I50,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.78500000000000003</v>
       </c>
       <c r="H50">
@@ -11568,17 +12004,17 @@
       <c r="C51" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="D51" s="27" t="s">
+      <c r="D51" t="s">
         <v>336</v>
       </c>
-      <c r="E51" s="27" t="s">
+      <c r="E51" t="s">
         <v>337</v>
       </c>
-      <c r="F51" s="28" t="s">
+      <c r="F51" s="27" t="s">
         <v>338</v>
       </c>
       <c r="G51" t="str">
-        <f>IF(I51&lt;0.001,"&lt; 0.001*",IF(I51&lt;0.05,CONCATENATE(ROUND(I51,3),"*"),ROUND(I51,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.025*</v>
       </c>
       <c r="H51">
@@ -11598,17 +12034,17 @@
       <c r="C52" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" t="s">
         <v>339</v>
       </c>
-      <c r="E52" s="27" t="s">
+      <c r="E52" t="s">
         <v>340</v>
       </c>
-      <c r="F52" s="28" t="s">
+      <c r="F52" s="27" t="s">
         <v>341</v>
       </c>
       <c r="G52" t="str">
-        <f>IF(I52&lt;0.001,"&lt; 0.001*",IF(I52&lt;0.05,CONCATENATE(ROUND(I52,3),"*"),ROUND(I52,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.016*</v>
       </c>
       <c r="H52">
@@ -11628,17 +12064,17 @@
       <c r="C53" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" t="s">
         <v>342</v>
       </c>
-      <c r="E53" s="27" t="s">
+      <c r="E53" t="s">
         <v>343</v>
       </c>
-      <c r="F53" s="28" t="s">
+      <c r="F53" s="27" t="s">
         <v>332</v>
       </c>
       <c r="G53">
-        <f>IF(I53&lt;0.001,"&lt; 0.001*",IF(I53&lt;0.05,CONCATENATE(ROUND(I53,3),"*"),ROUND(I53,3)))</f>
+        <f t="shared" si="5"/>
         <v>6.2E-2</v>
       </c>
       <c r="H53">
@@ -11658,17 +12094,17 @@
       <c r="C54" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="D54" s="27" t="s">
+      <c r="D54" t="s">
         <v>344</v>
       </c>
-      <c r="E54" s="27" t="s">
+      <c r="E54" t="s">
         <v>345</v>
       </c>
-      <c r="F54" s="28" t="s">
+      <c r="F54" s="27" t="s">
         <v>346</v>
       </c>
       <c r="G54">
-        <f>IF(I54&lt;0.001,"&lt; 0.001*",IF(I54&lt;0.05,CONCATENATE(ROUND(I54,3),"*"),ROUND(I54,3)))</f>
+        <f t="shared" si="5"/>
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="H54">
@@ -11688,17 +12124,17 @@
       <c r="C55" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="D55" s="27" t="s">
+      <c r="D55" t="s">
         <v>347</v>
       </c>
-      <c r="E55" s="27" t="s">
+      <c r="E55" t="s">
         <v>348</v>
       </c>
-      <c r="F55" s="28" t="s">
+      <c r="F55" s="27" t="s">
         <v>349</v>
       </c>
       <c r="G55" t="str">
-        <f>IF(I55&lt;0.001,"&lt; 0.001*",IF(I55&lt;0.05,CONCATENATE(ROUND(I55,3),"*"),ROUND(I55,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.044*</v>
       </c>
       <c r="H55">
@@ -11718,17 +12154,17 @@
       <c r="C56" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="D56" s="27" t="s">
+      <c r="D56" t="s">
         <v>350</v>
       </c>
-      <c r="E56" s="27" t="s">
+      <c r="E56" t="s">
         <v>351</v>
       </c>
-      <c r="F56" s="28" t="s">
+      <c r="F56" s="27" t="s">
         <v>352</v>
       </c>
       <c r="G56">
-        <f>IF(I56&lt;0.001,"&lt; 0.001*",IF(I56&lt;0.05,CONCATENATE(ROUND(I56,3),"*"),ROUND(I56,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.16500000000000001</v>
       </c>
       <c r="H56">
@@ -11748,17 +12184,17 @@
       <c r="C57" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" t="s">
         <v>353</v>
       </c>
-      <c r="E57" s="27" t="s">
+      <c r="E57" t="s">
         <v>354</v>
       </c>
-      <c r="F57" s="28" t="s">
+      <c r="F57" s="27" t="s">
         <v>355</v>
       </c>
       <c r="G57">
-        <f>IF(I57&lt;0.001,"&lt; 0.001*",IF(I57&lt;0.05,CONCATENATE(ROUND(I57,3),"*"),ROUND(I57,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="H57">
@@ -11778,17 +12214,17 @@
       <c r="C58" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="D58" s="27" t="s">
+      <c r="D58" t="s">
         <v>356</v>
       </c>
-      <c r="E58" s="27" t="s">
+      <c r="E58" t="s">
         <v>357</v>
       </c>
-      <c r="F58" s="28" t="s">
+      <c r="F58" s="27" t="s">
         <v>358</v>
       </c>
       <c r="G58">
-        <f>IF(I58&lt;0.001,"&lt; 0.001*",IF(I58&lt;0.05,CONCATENATE(ROUND(I58,3),"*"),ROUND(I58,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.11700000000000001</v>
       </c>
       <c r="H58">
@@ -11808,17 +12244,17 @@
       <c r="C59" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="D59" s="27" t="s">
+      <c r="D59" t="s">
         <v>359</v>
       </c>
-      <c r="E59" s="27" t="s">
+      <c r="E59" t="s">
         <v>360</v>
       </c>
-      <c r="F59" s="28" t="s">
+      <c r="F59" s="27" t="s">
         <v>361</v>
       </c>
       <c r="G59">
-        <f>IF(I59&lt;0.001,"&lt; 0.001*",IF(I59&lt;0.05,CONCATENATE(ROUND(I59,3),"*"),ROUND(I59,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.10199999999999999</v>
       </c>
       <c r="H59">
@@ -11838,17 +12274,17 @@
       <c r="C60" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" t="s">
         <v>362</v>
       </c>
-      <c r="E60" s="27" t="s">
+      <c r="E60" t="s">
         <v>363</v>
       </c>
-      <c r="F60" s="28" t="s">
+      <c r="F60" s="27" t="s">
         <v>364</v>
       </c>
       <c r="G60" t="str">
-        <f>IF(I60&lt;0.001,"&lt; 0.001*",IF(I60&lt;0.05,CONCATENATE(ROUND(I60,3),"*"),ROUND(I60,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.024*</v>
       </c>
       <c r="H60">
@@ -11865,20 +12301,20 @@
       <c r="B61" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="29" t="s">
         <v>365</v>
       </c>
-      <c r="E61" s="30" t="s">
+      <c r="E61" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="F61" s="31" t="s">
+      <c r="F61" s="30" t="s">
         <v>367</v>
       </c>
       <c r="G61" t="str">
-        <f>IF(I61&lt;0.001,"&lt; 0.001*",IF(I61&lt;0.05,CONCATENATE(ROUND(I61,3),"*"),ROUND(I61,3)))</f>
+        <f t="shared" si="5"/>
         <v>0.031*</v>
       </c>
       <c r="H61">
